--- a/03.QLDA/V314.xlsx
+++ b/03.QLDA/V314.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMECC JSC\Amecc 2\00. Overall Report\03.QLDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tool\Server_Leo_Nguyen\03.QLDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FE1F69-7674-43A7-897C-11E5FD4E1B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9867DD-84BE-48A2-9191-FE4C3FDD3FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
   </bookViews>
@@ -57,7 +57,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="66" r:id="rId2"/>
+    <pivotCache cacheId="6" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -70,8 +70,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -79,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="207">
   <si>
     <t>Gá lắp</t>
   </si>
@@ -688,6 +686,18 @@
   </si>
   <si>
     <t>V314-001</t>
+  </si>
+  <si>
+    <t>V314-CS-U1-006</t>
+  </si>
+  <si>
+    <t>V314-CS-U1-007</t>
+  </si>
+  <si>
+    <t>V314-005</t>
+  </si>
+  <si>
+    <t>V314-004</t>
   </si>
 </sst>
 </file>
@@ -695,11 +705,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1046,7 +1056,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1134,28 +1144,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1176,19 +1186,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1210,13 +1220,13 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -1244,16 +1254,16 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,7 +1335,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46275.91412465278" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="91" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Hiếu Nguyễn" refreshedDate="46293.609778240738" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="91" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A3:BA94" sheet="Progress"/>
   </cacheSource>
@@ -1383,10 +1393,10 @@
     <cacheField name="T'Qty" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="U.Weight" numFmtId="43">
+    <cacheField name="U.Weight" numFmtId="164">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1589.9799999999998" maxValue="23721.187999999995"/>
     </cacheField>
-    <cacheField name="T.Weight" numFmtId="43">
+    <cacheField name="T.Weight" numFmtId="164">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1589.9799999999998" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Profile" numFmtId="0">
@@ -1431,10 +1441,10 @@
     <cacheField name="DATE CPCL" numFmtId="14">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Hoàn thiện" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="21349.069199999998"/>
+    <cacheField name="Hoàn thiện" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999998"/>
     </cacheField>
-    <cacheField name="Còn lại" numFmtId="43">
+    <cacheField name="Còn lại" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Kế hoạch Tháng" numFmtId="0">
@@ -1443,7 +1453,7 @@
     <cacheField name="Nhận Phôi" numFmtId="9">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.05" maxValue="0.3"/>
     </cacheField>
-    <cacheField name="Khối lượng" numFmtId="164">
+    <cacheField name="Khối lượng" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="7116.3563999999978"/>
     </cacheField>
     <cacheField name="Ngày Gá" numFmtId="14">
@@ -1452,7 +1462,7 @@
     <cacheField name="SL Gá" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL Gá" numFmtId="43">
+    <cacheField name="KL Gá" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Ngày Hàn" numFmtId="14">
@@ -1461,7 +1471,7 @@
     <cacheField name="SL Hàn" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL Hàn" numFmtId="43">
+    <cacheField name="KL Hàn" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Ngày TH" numFmtId="14">
@@ -1470,29 +1480,29 @@
     <cacheField name="SL TH" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="KL TH" numFmtId="43">
+    <cacheField name="KL TH" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Số AFI" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Ngày NT" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-08-07T00:00:00" maxDate="2026-08-12T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-08-07T00:00:00" maxDate="2026-09-21T00:00:00"/>
     </cacheField>
     <cacheField name="SL NT" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL NT" numFmtId="43">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="11756.467999999999"/>
+    <cacheField name="KL NT" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Ngày BG" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-08-14T00:00:00" maxDate="2026-08-15T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-08-14T00:00:00" maxDate="2026-09-26T00:00:00"/>
     </cacheField>
     <cacheField name="SL BG" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL BG" numFmtId="43">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="11756.467999999999"/>
+    <cacheField name="KL BG" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Đơn vị nhận" numFmtId="0">
       <sharedItems containsBlank="1"/>
@@ -1652,8 +1662,8 @@
     <m/>
     <m/>
     <m/>
-    <n v="20479.887000000002"/>
-    <n v="2275.5429999999978"/>
+    <n v="22755.430000000004"/>
+    <n v="0"/>
     <m/>
     <n v="0.3"/>
     <n v="6826.6289999999999"/>
@@ -1666,15 +1676,15 @@
     <m/>
     <m/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <s v="V314-CS-U1-007"/>
+    <d v="2026-09-20T00:00:00"/>
+    <n v="1"/>
+    <n v="22755.43"/>
+    <d v="2026-09-25T00:00:00"/>
+    <n v="1"/>
+    <n v="22755.43"/>
     <s v="PAC"/>
-    <m/>
+    <s v="V314-5"/>
   </r>
   <r>
     <n v="4"/>
@@ -2147,8 +2157,8 @@
     <m/>
     <m/>
     <m/>
-    <n v="21349.069199999998"/>
-    <n v="2372.1187999999966"/>
+    <n v="23721.187999999998"/>
+    <n v="0"/>
     <m/>
     <n v="0.3"/>
     <n v="7116.3563999999978"/>
@@ -2161,15 +2171,15 @@
     <m/>
     <m/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <s v="V314-CS-U1-006"/>
+    <d v="2026-09-18T00:00:00"/>
+    <n v="1"/>
+    <n v="23721.187999999995"/>
+    <d v="2026-09-25T00:00:00"/>
+    <n v="1"/>
+    <n v="23721.187999999995"/>
     <s v="PAC"/>
-    <m/>
+    <s v="V314-4"/>
   </r>
   <r>
     <n v="13"/>
@@ -6520,7 +6530,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="66" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BF3:BH9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="53">
     <pivotField showAll="0"/>
@@ -6573,27 +6583,27 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
@@ -6635,7 +6645,7 @@
   </colItems>
   <dataFields count="2">
     <dataField name="Sum of T.Weight" fld="15" baseField="1" baseItem="0"/>
-    <dataField name="Sum of KL Gá" fld="37" baseField="0" baseItem="0" numFmtId="43"/>
+    <dataField name="Sum of KL Gá" fld="37" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -6968,7 +6978,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:BH95"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -7018,7 +7028,7 @@
     <col min="60" max="60" width="14.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:60" ht="25.5" customHeight="1" thickTop="1">
       <c r="A1" s="1" t="str">
         <f>"DỰ ÁN:"&amp;B4</f>
         <v>DỰ ÁN:V314</v>
@@ -7089,7 +7099,7 @@
       <c r="BC1" s="48"/>
       <c r="BD1" s="48"/>
     </row>
-    <row r="2" spans="1:60" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:60" ht="25.5" customHeight="1" thickBot="1">
       <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
@@ -7114,7 +7124,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="51">
         <f ca="1">IF(WEEKDAY(TODAY()-1)=1,TODAY()-2,TODAY()-1)</f>
-        <v>46274</v>
+        <v>46291</v>
       </c>
       <c r="T2" s="13" t="s">
         <v>40</v>
@@ -7170,20 +7180,20 @@
       <c r="AT2" s="17"/>
       <c r="AU2" s="67">
         <f>SUBTOTAL(9,AU4:AU94)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV2" s="68">
         <f>SUBTOTAL(9,AV4:AV94)</f>
-        <v>64842.223999999995</v>
+        <v>111318.84199999999</v>
       </c>
       <c r="AW2" s="16"/>
       <c r="AX2" s="67">
         <f>SUBTOTAL(9,AX4:AX94)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY2" s="67">
         <f>SUBTOTAL(9,AY4:AY94)</f>
-        <v>64842.223999999995</v>
+        <v>111318.84199999999</v>
       </c>
       <c r="AZ2" s="17"/>
       <c r="BA2" s="18" t="str">
@@ -7194,7 +7204,7 @@
       <c r="BC2" s="48"/>
       <c r="BD2" s="48"/>
     </row>
-    <row r="3" spans="1:60" ht="27" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:60" ht="27" customHeight="1" thickTop="1">
       <c r="A3" s="19" t="s">
         <v>7</v>
       </c>
@@ -7373,7 +7383,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:60">
       <c r="A4" s="24">
         <f>IF(B4="","",SUBTOTAL(3,$B$4:B4))</f>
         <v>1</v>
@@ -7506,7 +7516,7 @@
         <v>189764.41100000002</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:60">
       <c r="A5" s="24">
         <f>IF(B5="","",SUBTOTAL(3,$B$4:B5))</f>
         <v>2</v>
@@ -7639,7 +7649,7 @@
         <v>189764.41100000002</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:60">
       <c r="A6" s="24">
         <f>IF(B6="","",SUBTOTAL(3,$B$4:B6))</f>
         <v>3</v>
@@ -7702,11 +7712,11 @@
       <c r="AD6" s="54"/>
       <c r="AE6" s="31">
         <f t="shared" si="1"/>
-        <v>20479.887000000002</v>
+        <v>22755.430000000004</v>
       </c>
       <c r="AF6" s="32">
         <f t="shared" si="2"/>
-        <v>2275.5429999999978</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="30"/>
       <c r="AH6" s="33">
@@ -7742,23 +7752,35 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AS6" s="27"/>
-      <c r="AT6" s="37"/>
-      <c r="AU6" s="30"/>
+      <c r="AS6" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="AT6" s="37">
+        <v>46285</v>
+      </c>
+      <c r="AU6" s="30">
+        <v>1</v>
+      </c>
       <c r="AV6" s="36">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AW6" s="35"/>
-      <c r="AX6" s="30"/>
+        <v>22755.43</v>
+      </c>
+      <c r="AW6" s="35">
+        <v>46290</v>
+      </c>
+      <c r="AX6" s="30">
+        <v>1</v>
+      </c>
       <c r="AY6" s="32">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>22755.43</v>
       </c>
       <c r="AZ6" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="BA6" s="63"/>
+      <c r="BA6" s="63" t="s">
+        <v>205</v>
+      </c>
       <c r="BB6" s="71"/>
       <c r="BC6" s="71"/>
       <c r="BD6" s="71"/>
@@ -7772,7 +7794,7 @@
         <v>189764.41100000002</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:60">
       <c r="A7" s="24">
         <f>IF(B7="","",SUBTOTAL(3,$B$4:B7))</f>
         <v>4</v>
@@ -7905,7 +7927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:60">
       <c r="A8" s="24">
         <f>IF(B8="","",SUBTOTAL(3,$B$4:B8))</f>
         <v>5</v>
@@ -8038,7 +8060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:60">
       <c r="A9" s="24">
         <f>IF(B9="","",SUBTOTAL(3,$B$4:B9))</f>
         <v>6</v>
@@ -8171,7 +8193,7 @@
         <v>189764.41100000002</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:60">
       <c r="A10" s="24">
         <f>IF(B10="","",SUBTOTAL(3,$B$4:B10))</f>
         <v>7</v>
@@ -8295,7 +8317,7 @@
       <c r="BC10" s="71"/>
       <c r="BD10" s="71"/>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:60">
       <c r="A11" s="24">
         <f>IF(B11="","",SUBTOTAL(3,$B$4:B11))</f>
         <v>8</v>
@@ -8419,7 +8441,7 @@
       <c r="BC11" s="71"/>
       <c r="BD11" s="71"/>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:60">
       <c r="A12" s="24">
         <f>IF(B12="","",SUBTOTAL(3,$B$4:B12))</f>
         <v>9</v>
@@ -8543,7 +8565,7 @@
       <c r="BC12" s="71"/>
       <c r="BD12" s="71"/>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:60">
       <c r="A13" s="24">
         <f>IF(B13="","",SUBTOTAL(3,$B$4:B13))</f>
         <v>10</v>
@@ -8667,7 +8689,7 @@
       <c r="BC13" s="71"/>
       <c r="BD13" s="71"/>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:60">
       <c r="A14" s="24">
         <f>IF(B14="","",SUBTOTAL(3,$B$4:B14))</f>
         <v>11</v>
@@ -8791,7 +8813,7 @@
       <c r="BC14" s="71"/>
       <c r="BD14" s="71"/>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:60">
       <c r="A15" s="24">
         <f>IF(B15="","",SUBTOTAL(3,$B$4:B15))</f>
         <v>12</v>
@@ -8854,11 +8876,11 @@
       <c r="AD15" s="54"/>
       <c r="AE15" s="31">
         <f t="shared" si="10"/>
-        <v>21349.069199999998</v>
+        <v>23721.187999999998</v>
       </c>
       <c r="AF15" s="32">
         <f t="shared" si="11"/>
-        <v>2372.1187999999966</v>
+        <v>0</v>
       </c>
       <c r="AG15" s="30"/>
       <c r="AH15" s="33">
@@ -8894,28 +8916,40 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AS15" s="27"/>
-      <c r="AT15" s="37"/>
-      <c r="AU15" s="30"/>
+      <c r="AS15" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT15" s="37">
+        <v>46283</v>
+      </c>
+      <c r="AU15" s="30">
+        <v>1</v>
+      </c>
       <c r="AV15" s="36">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AW15" s="35"/>
-      <c r="AX15" s="30"/>
+        <v>23721.187999999995</v>
+      </c>
+      <c r="AW15" s="35">
+        <v>46290</v>
+      </c>
+      <c r="AX15" s="30">
+        <v>1</v>
+      </c>
       <c r="AY15" s="32">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>23721.187999999995</v>
       </c>
       <c r="AZ15" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="BA15" s="63"/>
+      <c r="BA15" s="63" t="s">
+        <v>206</v>
+      </c>
       <c r="BB15" s="71"/>
       <c r="BC15" s="71"/>
       <c r="BD15" s="71"/>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:60">
       <c r="A16" s="24">
         <f>IF(B16="","",SUBTOTAL(3,$B$4:B16))</f>
         <v>13</v>
@@ -9039,7 +9073,7 @@
       <c r="BC16" s="71"/>
       <c r="BD16" s="71"/>
     </row>
-    <row r="17" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:56">
       <c r="A17" s="24">
         <f>IF(B17="","",SUBTOTAL(3,$B$4:B17))</f>
         <v>14</v>
@@ -9163,7 +9197,7 @@
       <c r="BC17" s="71"/>
       <c r="BD17" s="71"/>
     </row>
-    <row r="18" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:56">
       <c r="A18" s="24">
         <f>IF(B18="","",SUBTOTAL(3,$B$4:B18))</f>
         <v>15</v>
@@ -9287,7 +9321,7 @@
       <c r="BC18" s="71"/>
       <c r="BD18" s="71"/>
     </row>
-    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:56">
       <c r="A19" s="24">
         <f>IF(B19="","",SUBTOTAL(3,$B$4:B19))</f>
         <v>16</v>
@@ -9411,7 +9445,7 @@
       <c r="BC19" s="71"/>
       <c r="BD19" s="71"/>
     </row>
-    <row r="20" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:56">
       <c r="A20" s="24">
         <f>IF(B20="","",SUBTOTAL(3,$B$4:B20))</f>
         <v>17</v>
@@ -9547,7 +9581,7 @@
       <c r="BC20" s="71"/>
       <c r="BD20" s="71"/>
     </row>
-    <row r="21" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:56">
       <c r="A21" s="24">
         <f>IF(B21="","",SUBTOTAL(3,$B$4:B21))</f>
         <v>18</v>
@@ -9683,7 +9717,7 @@
       <c r="BC21" s="71"/>
       <c r="BD21" s="71"/>
     </row>
-    <row r="22" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:56">
       <c r="A22" s="24">
         <f>IF(B22="","",SUBTOTAL(3,$B$4:B22))</f>
         <v>19</v>
@@ -9819,7 +9853,7 @@
       <c r="BC22" s="71"/>
       <c r="BD22" s="71"/>
     </row>
-    <row r="23" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:56">
       <c r="A23" s="24">
         <f>IF(B23="","",SUBTOTAL(3,$B$4:B23))</f>
         <v>20</v>
@@ -9955,7 +9989,7 @@
       <c r="BC23" s="71"/>
       <c r="BD23" s="71"/>
     </row>
-    <row r="24" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:56">
       <c r="A24" s="24">
         <f>IF(B24="","",SUBTOTAL(3,$B$4:B24))</f>
         <v>21</v>
@@ -10091,7 +10125,7 @@
       <c r="BC24" s="71"/>
       <c r="BD24" s="71"/>
     </row>
-    <row r="25" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:56">
       <c r="A25" s="24">
         <f>IF(B25="","",SUBTOTAL(3,$B$4:B25))</f>
         <v>22</v>
@@ -10227,7 +10261,7 @@
       <c r="BC25" s="71"/>
       <c r="BD25" s="71"/>
     </row>
-    <row r="26" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:56">
       <c r="A26" s="24">
         <f>IF(B26="","",SUBTOTAL(3,$B$4:B26))</f>
         <v>23</v>
@@ -10341,7 +10375,7 @@
       <c r="BC26" s="71"/>
       <c r="BD26" s="71"/>
     </row>
-    <row r="27" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:56">
       <c r="A27" s="24">
         <f>IF(B27="","",SUBTOTAL(3,$B$4:B27))</f>
         <v>24</v>
@@ -10457,7 +10491,7 @@
       <c r="BC27" s="71"/>
       <c r="BD27" s="71"/>
     </row>
-    <row r="28" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:56">
       <c r="A28" s="24">
         <f>IF(B28="","",SUBTOTAL(3,$B$4:B28))</f>
         <v>25</v>
@@ -10573,7 +10607,7 @@
       <c r="BC28" s="71"/>
       <c r="BD28" s="71"/>
     </row>
-    <row r="29" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:56">
       <c r="A29" s="24">
         <f>IF(B29="","",SUBTOTAL(3,$B$4:B29))</f>
         <v>26</v>
@@ -10689,7 +10723,7 @@
       <c r="BC29" s="71"/>
       <c r="BD29" s="71"/>
     </row>
-    <row r="30" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:56">
       <c r="A30" s="24">
         <f>IF(B30="","",SUBTOTAL(3,$B$4:B30))</f>
         <v>27</v>
@@ -10805,7 +10839,7 @@
       <c r="BC30" s="71"/>
       <c r="BD30" s="71"/>
     </row>
-    <row r="31" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:56">
       <c r="A31" s="24">
         <f>IF(B31="","",SUBTOTAL(3,$B$4:B31))</f>
         <v>28</v>
@@ -10921,7 +10955,7 @@
       <c r="BC31" s="71"/>
       <c r="BD31" s="71"/>
     </row>
-    <row r="32" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:56">
       <c r="A32" s="24">
         <f>IF(B32="","",SUBTOTAL(3,$B$4:B32))</f>
         <v>29</v>
@@ -11037,7 +11071,7 @@
       <c r="BC32" s="71"/>
       <c r="BD32" s="71"/>
     </row>
-    <row r="33" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:56">
       <c r="A33" s="24">
         <f>IF(B33="","",SUBTOTAL(3,$B$4:B33))</f>
         <v>30</v>
@@ -11153,7 +11187,7 @@
       <c r="BC33" s="71"/>
       <c r="BD33" s="71"/>
     </row>
-    <row r="34" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:56">
       <c r="A34" s="24">
         <f>IF(B34="","",SUBTOTAL(3,$B$4:B34))</f>
         <v>31</v>
@@ -11269,7 +11303,7 @@
       <c r="BC34" s="71"/>
       <c r="BD34" s="71"/>
     </row>
-    <row r="35" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:56">
       <c r="A35" s="24">
         <f>IF(B35="","",SUBTOTAL(3,$B$4:B35))</f>
         <v>32</v>
@@ -11385,7 +11419,7 @@
       <c r="BC35" s="71"/>
       <c r="BD35" s="71"/>
     </row>
-    <row r="36" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:56">
       <c r="A36" s="24">
         <f>IF(B36="","",SUBTOTAL(3,$B$4:B36))</f>
         <v>33</v>
@@ -11501,7 +11535,7 @@
       <c r="BC36" s="71"/>
       <c r="BD36" s="71"/>
     </row>
-    <row r="37" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:56">
       <c r="A37" s="24">
         <f>IF(B37="","",SUBTOTAL(3,$B$4:B37))</f>
         <v>34</v>
@@ -11617,7 +11651,7 @@
       <c r="BC37" s="71"/>
       <c r="BD37" s="71"/>
     </row>
-    <row r="38" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:56">
       <c r="A38" s="24">
         <f>IF(B38="","",SUBTOTAL(3,$B$4:B38))</f>
         <v>35</v>
@@ -11733,7 +11767,7 @@
       <c r="BC38" s="71"/>
       <c r="BD38" s="71"/>
     </row>
-    <row r="39" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:56">
       <c r="A39" s="24">
         <f>IF(B39="","",SUBTOTAL(3,$B$4:B39))</f>
         <v>36</v>
@@ -11849,7 +11883,7 @@
       <c r="BC39" s="71"/>
       <c r="BD39" s="71"/>
     </row>
-    <row r="40" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:56">
       <c r="A40" s="24">
         <f>IF(B40="","",SUBTOTAL(3,$B$4:B40))</f>
         <v>37</v>
@@ -11965,7 +11999,7 @@
       <c r="BC40" s="71"/>
       <c r="BD40" s="71"/>
     </row>
-    <row r="41" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:56">
       <c r="A41" s="24">
         <f>IF(B41="","",SUBTOTAL(3,$B$4:B41))</f>
         <v>38</v>
@@ -12081,7 +12115,7 @@
       <c r="BC41" s="71"/>
       <c r="BD41" s="71"/>
     </row>
-    <row r="42" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:56">
       <c r="A42" s="24">
         <f>IF(B42="","",SUBTOTAL(3,$B$4:B42))</f>
         <v>39</v>
@@ -12197,7 +12231,7 @@
       <c r="BC42" s="71"/>
       <c r="BD42" s="71"/>
     </row>
-    <row r="43" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:56">
       <c r="A43" s="24">
         <f>IF(B43="","",SUBTOTAL(3,$B$4:B43))</f>
         <v>40</v>
@@ -12313,7 +12347,7 @@
       <c r="BC43" s="71"/>
       <c r="BD43" s="71"/>
     </row>
-    <row r="44" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:56">
       <c r="A44" s="24">
         <f>IF(B44="","",SUBTOTAL(3,$B$4:B44))</f>
         <v>41</v>
@@ -12429,7 +12463,7 @@
       <c r="BC44" s="71"/>
       <c r="BD44" s="71"/>
     </row>
-    <row r="45" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:56">
       <c r="A45" s="24">
         <f>IF(B45="","",SUBTOTAL(3,$B$4:B45))</f>
         <v>42</v>
@@ -12545,7 +12579,7 @@
       <c r="BC45" s="71"/>
       <c r="BD45" s="71"/>
     </row>
-    <row r="46" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:56">
       <c r="A46" s="24">
         <f>IF(B46="","",SUBTOTAL(3,$B$4:B46))</f>
         <v>43</v>
@@ -12661,7 +12695,7 @@
       <c r="BC46" s="71"/>
       <c r="BD46" s="71"/>
     </row>
-    <row r="47" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:56">
       <c r="A47" s="24">
         <f>IF(B47="","",SUBTOTAL(3,$B$4:B47))</f>
         <v>44</v>
@@ -12777,7 +12811,7 @@
       <c r="BC47" s="71"/>
       <c r="BD47" s="71"/>
     </row>
-    <row r="48" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:56">
       <c r="A48" s="24">
         <f>IF(B48="","",SUBTOTAL(3,$B$4:B48))</f>
         <v>45</v>
@@ -12893,7 +12927,7 @@
       <c r="BC48" s="71"/>
       <c r="BD48" s="71"/>
     </row>
-    <row r="49" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:56">
       <c r="A49" s="24">
         <f>IF(B49="","",SUBTOTAL(3,$B$4:B49))</f>
         <v>46</v>
@@ -13009,7 +13043,7 @@
       <c r="BC49" s="71"/>
       <c r="BD49" s="71"/>
     </row>
-    <row r="50" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:56">
       <c r="A50" s="24">
         <f>IF(B50="","",SUBTOTAL(3,$B$4:B50))</f>
         <v>47</v>
@@ -13125,7 +13159,7 @@
       <c r="BC50" s="71"/>
       <c r="BD50" s="71"/>
     </row>
-    <row r="51" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:56">
       <c r="A51" s="24">
         <f>IF(B51="","",SUBTOTAL(3,$B$4:B51))</f>
         <v>48</v>
@@ -13241,7 +13275,7 @@
       <c r="BC51" s="71"/>
       <c r="BD51" s="71"/>
     </row>
-    <row r="52" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:56">
       <c r="A52" s="24">
         <f>IF(B52="","",SUBTOTAL(3,$B$4:B52))</f>
         <v>49</v>
@@ -13357,7 +13391,7 @@
       <c r="BC52" s="71"/>
       <c r="BD52" s="71"/>
     </row>
-    <row r="53" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:56">
       <c r="A53" s="24">
         <f>IF(B53="","",SUBTOTAL(3,$B$4:B53))</f>
         <v>50</v>
@@ -13473,7 +13507,7 @@
       <c r="BC53" s="71"/>
       <c r="BD53" s="71"/>
     </row>
-    <row r="54" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:56">
       <c r="A54" s="24">
         <f>IF(B54="","",SUBTOTAL(3,$B$4:B54))</f>
         <v>51</v>
@@ -13589,7 +13623,7 @@
       <c r="BC54" s="71"/>
       <c r="BD54" s="71"/>
     </row>
-    <row r="55" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:56">
       <c r="A55" s="24">
         <f>IF(B55="","",SUBTOTAL(3,$B$4:B55))</f>
         <v>52</v>
@@ -13705,7 +13739,7 @@
       <c r="BC55" s="71"/>
       <c r="BD55" s="71"/>
     </row>
-    <row r="56" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:56">
       <c r="A56" s="24">
         <f>IF(B56="","",SUBTOTAL(3,$B$4:B56))</f>
         <v>53</v>
@@ -13821,7 +13855,7 @@
       <c r="BC56" s="71"/>
       <c r="BD56" s="71"/>
     </row>
-    <row r="57" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:56">
       <c r="A57" s="24">
         <f>IF(B57="","",SUBTOTAL(3,$B$4:B57))</f>
         <v>54</v>
@@ -13937,7 +13971,7 @@
       <c r="BC57" s="71"/>
       <c r="BD57" s="71"/>
     </row>
-    <row r="58" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:56">
       <c r="A58" s="24">
         <f>IF(B58="","",SUBTOTAL(3,$B$4:B58))</f>
         <v>55</v>
@@ -14053,7 +14087,7 @@
       <c r="BC58" s="71"/>
       <c r="BD58" s="71"/>
     </row>
-    <row r="59" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:56">
       <c r="A59" s="24">
         <f>IF(B59="","",SUBTOTAL(3,$B$4:B59))</f>
         <v>56</v>
@@ -14169,7 +14203,7 @@
       <c r="BC59" s="71"/>
       <c r="BD59" s="71"/>
     </row>
-    <row r="60" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:56">
       <c r="A60" s="24">
         <f>IF(B60="","",SUBTOTAL(3,$B$4:B60))</f>
         <v>57</v>
@@ -14285,7 +14319,7 @@
       <c r="BC60" s="71"/>
       <c r="BD60" s="71"/>
     </row>
-    <row r="61" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:56">
       <c r="A61" s="24">
         <f>IF(B61="","",SUBTOTAL(3,$B$4:B61))</f>
         <v>58</v>
@@ -14401,7 +14435,7 @@
       <c r="BC61" s="71"/>
       <c r="BD61" s="71"/>
     </row>
-    <row r="62" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:56">
       <c r="A62" s="24">
         <f>IF(B62="","",SUBTOTAL(3,$B$4:B62))</f>
         <v>59</v>
@@ -14517,7 +14551,7 @@
       <c r="BC62" s="71"/>
       <c r="BD62" s="71"/>
     </row>
-    <row r="63" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:56">
       <c r="A63" s="24">
         <f>IF(B63="","",SUBTOTAL(3,$B$4:B63))</f>
         <v>60</v>
@@ -14633,7 +14667,7 @@
       <c r="BC63" s="71"/>
       <c r="BD63" s="71"/>
     </row>
-    <row r="64" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:56">
       <c r="A64" s="24">
         <f>IF(B64="","",SUBTOTAL(3,$B$4:B64))</f>
         <v>61</v>
@@ -14749,7 +14783,7 @@
       <c r="BC64" s="71"/>
       <c r="BD64" s="71"/>
     </row>
-    <row r="65" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:56">
       <c r="A65" s="24">
         <f>IF(B65="","",SUBTOTAL(3,$B$4:B65))</f>
         <v>62</v>
@@ -14865,7 +14899,7 @@
       <c r="BC65" s="71"/>
       <c r="BD65" s="71"/>
     </row>
-    <row r="66" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:56">
       <c r="A66" s="24">
         <f>IF(B66="","",SUBTOTAL(3,$B$4:B66))</f>
         <v>63</v>
@@ -14979,7 +15013,7 @@
       <c r="BC66" s="71"/>
       <c r="BD66" s="71"/>
     </row>
-    <row r="67" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:56">
       <c r="A67" s="24">
         <f>IF(B67="","",SUBTOTAL(3,$B$4:B67))</f>
         <v>64</v>
@@ -15095,7 +15129,7 @@
       <c r="BC67" s="71"/>
       <c r="BD67" s="71"/>
     </row>
-    <row r="68" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:56">
       <c r="A68" s="24">
         <f>IF(B68="","",SUBTOTAL(3,$B$4:B68))</f>
         <v>65</v>
@@ -15211,7 +15245,7 @@
       <c r="BC68" s="71"/>
       <c r="BD68" s="71"/>
     </row>
-    <row r="69" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:56">
       <c r="A69" s="24">
         <f>IF(B69="","",SUBTOTAL(3,$B$4:B69))</f>
         <v>66</v>
@@ -15327,7 +15361,7 @@
       <c r="BC69" s="71"/>
       <c r="BD69" s="71"/>
     </row>
-    <row r="70" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:56">
       <c r="A70" s="24">
         <f>IF(B70="","",SUBTOTAL(3,$B$4:B70))</f>
         <v>67</v>
@@ -15443,7 +15477,7 @@
       <c r="BC70" s="71"/>
       <c r="BD70" s="71"/>
     </row>
-    <row r="71" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:56">
       <c r="A71" s="24">
         <f>IF(B71="","",SUBTOTAL(3,$B$4:B71))</f>
         <v>68</v>
@@ -15559,7 +15593,7 @@
       <c r="BC71" s="71"/>
       <c r="BD71" s="71"/>
     </row>
-    <row r="72" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:56">
       <c r="A72" s="24">
         <f>IF(B72="","",SUBTOTAL(3,$B$4:B72))</f>
         <v>69</v>
@@ -15675,7 +15709,7 @@
       <c r="BC72" s="71"/>
       <c r="BD72" s="71"/>
     </row>
-    <row r="73" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:56">
       <c r="A73" s="24" t="str">
         <f>IF(B73="","",SUBTOTAL(3,$B$4:B73))</f>
         <v/>
@@ -15763,7 +15797,7 @@
       <c r="BC73" s="71"/>
       <c r="BD73" s="71"/>
     </row>
-    <row r="74" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:56">
       <c r="A74" s="24" t="str">
         <f>IF(B74="","",SUBTOTAL(3,$B$4:B74))</f>
         <v/>
@@ -15851,7 +15885,7 @@
       <c r="BC74" s="71"/>
       <c r="BD74" s="71"/>
     </row>
-    <row r="75" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:56">
       <c r="A75" s="24" t="str">
         <f>IF(B75="","",SUBTOTAL(3,$B$4:B75))</f>
         <v/>
@@ -15939,7 +15973,7 @@
       <c r="BC75" s="71"/>
       <c r="BD75" s="71"/>
     </row>
-    <row r="76" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:56">
       <c r="A76" s="24" t="str">
         <f>IF(B76="","",SUBTOTAL(3,$B$4:B76))</f>
         <v/>
@@ -16027,7 +16061,7 @@
       <c r="BC76" s="71"/>
       <c r="BD76" s="71"/>
     </row>
-    <row r="77" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:56">
       <c r="A77" s="24" t="str">
         <f>IF(B77="","",SUBTOTAL(3,$B$4:B77))</f>
         <v/>
@@ -16115,7 +16149,7 @@
       <c r="BC77" s="71"/>
       <c r="BD77" s="71"/>
     </row>
-    <row r="78" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:56">
       <c r="A78" s="24" t="str">
         <f>IF(B78="","",SUBTOTAL(3,$B$4:B78))</f>
         <v/>
@@ -16203,7 +16237,7 @@
       <c r="BC78" s="71"/>
       <c r="BD78" s="71"/>
     </row>
-    <row r="79" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:56">
       <c r="A79" s="24" t="str">
         <f>IF(B79="","",SUBTOTAL(3,$B$4:B79))</f>
         <v/>
@@ -16291,7 +16325,7 @@
       <c r="BC79" s="71"/>
       <c r="BD79" s="71"/>
     </row>
-    <row r="80" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:56">
       <c r="A80" s="24" t="str">
         <f>IF(B80="","",SUBTOTAL(3,$B$4:B80))</f>
         <v/>
@@ -16379,7 +16413,7 @@
       <c r="BC80" s="71"/>
       <c r="BD80" s="71"/>
     </row>
-    <row r="81" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:56">
       <c r="A81" s="24" t="str">
         <f>IF(B81="","",SUBTOTAL(3,$B$4:B81))</f>
         <v/>
@@ -16467,7 +16501,7 @@
       <c r="BC81" s="71"/>
       <c r="BD81" s="71"/>
     </row>
-    <row r="82" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:56">
       <c r="A82" s="24" t="str">
         <f>IF(B82="","",SUBTOTAL(3,$B$4:B82))</f>
         <v/>
@@ -16555,7 +16589,7 @@
       <c r="BC82" s="71"/>
       <c r="BD82" s="71"/>
     </row>
-    <row r="83" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:56">
       <c r="A83" s="24" t="str">
         <f>IF(B83="","",SUBTOTAL(3,$B$4:B83))</f>
         <v/>
@@ -16643,7 +16677,7 @@
       <c r="BC83" s="71"/>
       <c r="BD83" s="71"/>
     </row>
-    <row r="84" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:56">
       <c r="A84" s="24" t="str">
         <f>IF(B84="","",SUBTOTAL(3,$B$4:B84))</f>
         <v/>
@@ -16731,7 +16765,7 @@
       <c r="BC84" s="71"/>
       <c r="BD84" s="71"/>
     </row>
-    <row r="85" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:56">
       <c r="A85" s="24" t="str">
         <f>IF(B85="","",SUBTOTAL(3,$B$4:B85))</f>
         <v/>
@@ -16819,7 +16853,7 @@
       <c r="BC85" s="71"/>
       <c r="BD85" s="71"/>
     </row>
-    <row r="86" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:56">
       <c r="A86" s="24" t="str">
         <f>IF(B86="","",SUBTOTAL(3,$B$4:B86))</f>
         <v/>
@@ -16907,7 +16941,7 @@
       <c r="BC86" s="71"/>
       <c r="BD86" s="71"/>
     </row>
-    <row r="87" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:56">
       <c r="A87" s="24" t="str">
         <f>IF(B87="","",SUBTOTAL(3,$B$4:B87))</f>
         <v/>
@@ -16995,7 +17029,7 @@
       <c r="BC87" s="71"/>
       <c r="BD87" s="71"/>
     </row>
-    <row r="88" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:56">
       <c r="A88" s="24" t="str">
         <f>IF(B88="","",SUBTOTAL(3,$B$4:B88))</f>
         <v/>
@@ -17083,7 +17117,7 @@
       <c r="BC88" s="71"/>
       <c r="BD88" s="71"/>
     </row>
-    <row r="89" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:56">
       <c r="A89" s="24" t="str">
         <f>IF(B89="","",SUBTOTAL(3,$B$4:B89))</f>
         <v/>
@@ -17171,7 +17205,7 @@
       <c r="BC89" s="71"/>
       <c r="BD89" s="71"/>
     </row>
-    <row r="90" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:56">
       <c r="A90" s="24" t="str">
         <f>IF(B90="","",SUBTOTAL(3,$B$4:B90))</f>
         <v/>
@@ -17259,7 +17293,7 @@
       <c r="BC90" s="71"/>
       <c r="BD90" s="71"/>
     </row>
-    <row r="91" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:56">
       <c r="A91" s="24" t="str">
         <f>IF(B91="","",SUBTOTAL(3,$B$4:B91))</f>
         <v/>
@@ -17347,7 +17381,7 @@
       <c r="BC91" s="71"/>
       <c r="BD91" s="71"/>
     </row>
-    <row r="92" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:56">
       <c r="A92" s="24" t="str">
         <f>IF(B92="","",SUBTOTAL(3,$B$4:B92))</f>
         <v/>
@@ -17435,7 +17469,7 @@
       <c r="BC92" s="71"/>
       <c r="BD92" s="71"/>
     </row>
-    <row r="93" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:56">
       <c r="A93" s="24" t="str">
         <f>IF(B93="","",SUBTOTAL(3,$B$4:B93))</f>
         <v/>
@@ -17523,7 +17557,7 @@
       <c r="BC93" s="71"/>
       <c r="BD93" s="71"/>
     </row>
-    <row r="94" spans="1:56" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:56" ht="16.5" thickBot="1">
       <c r="A94" s="38" t="str">
         <f>IF(B94="","",SUBTOTAL(3,$B$4:B94))</f>
         <v/>
@@ -17611,7 +17645,7 @@
       <c r="BC94" s="71"/>
       <c r="BD94" s="71"/>
     </row>
-    <row r="95" spans="1:56" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:56" ht="16.5" thickTop="1"/>
   </sheetData>
   <autoFilter ref="A3:BD94" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}"/>
   <conditionalFormatting sqref="A4:AG94 AJ4:AL94">

--- a/03.QLDA/V314.xlsx
+++ b/03.QLDA/V314.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tool\Server_Leo_Nguyen\03.QLDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMECC JSC\Amecc 2\00. Overall Report\03.QLDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9867DD-84BE-48A2-9191-FE4C3FDD3FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7065DA-D6D0-450C-AFD0-3B5C4B67F9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
     <definedName name="ㅋㅋㅋㅋㅋㅋㅋㅋㅋ" hidden="1">#REF!</definedName>
     <definedName name="ㅌㅊㅍㅌㅊㅍㅌㅋㅊㅍㅌ" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <pivotCaches>
     <pivotCache cacheId="6" r:id="rId2"/>
   </pivotCaches>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="208">
   <si>
     <t>Gá lắp</t>
   </si>
@@ -698,6 +698,9 @@
   </si>
   <si>
     <t>V314-004</t>
+  </si>
+  <si>
+    <t>S4</t>
   </si>
 </sst>
 </file>
@@ -705,11 +708,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1056,7 +1059,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1144,28 +1147,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1186,19 +1189,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1220,13 +1223,13 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -1254,16 +1257,16 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1335,7 +1338,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Hiếu Nguyễn" refreshedDate="46293.609778240738" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="91" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46295.790670949071" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="91" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A3:BA94" sheet="Progress"/>
   </cacheSource>
@@ -1393,10 +1396,10 @@
     <cacheField name="T'Qty" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="U.Weight" numFmtId="164">
+    <cacheField name="U.Weight" numFmtId="43">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1589.9799999999998" maxValue="23721.187999999995"/>
     </cacheField>
-    <cacheField name="T.Weight" numFmtId="164">
+    <cacheField name="T.Weight" numFmtId="43">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1589.9799999999998" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Profile" numFmtId="0">
@@ -1441,10 +1444,10 @@
     <cacheField name="DATE CPCL" numFmtId="14">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Hoàn thiện" numFmtId="165">
+    <cacheField name="Hoàn thiện" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999998"/>
     </cacheField>
-    <cacheField name="Còn lại" numFmtId="164">
+    <cacheField name="Còn lại" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Kế hoạch Tháng" numFmtId="0">
@@ -1453,7 +1456,7 @@
     <cacheField name="Nhận Phôi" numFmtId="9">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.05" maxValue="0.3"/>
     </cacheField>
-    <cacheField name="Khối lượng" numFmtId="165">
+    <cacheField name="Khối lượng" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="7116.3563999999978"/>
     </cacheField>
     <cacheField name="Ngày Gá" numFmtId="14">
@@ -1462,7 +1465,7 @@
     <cacheField name="SL Gá" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL Gá" numFmtId="164">
+    <cacheField name="KL Gá" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Ngày Hàn" numFmtId="14">
@@ -1471,7 +1474,7 @@
     <cacheField name="SL Hàn" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL Hàn" numFmtId="164">
+    <cacheField name="KL Hàn" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Ngày TH" numFmtId="14">
@@ -1480,7 +1483,7 @@
     <cacheField name="SL TH" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="KL TH" numFmtId="164">
+    <cacheField name="KL TH" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Số AFI" numFmtId="0">
@@ -1492,7 +1495,7 @@
     <cacheField name="SL NT" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL NT" numFmtId="164">
+    <cacheField name="KL NT" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Ngày BG" numFmtId="14">
@@ -1501,7 +1504,7 @@
     <cacheField name="SL BG" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL BG" numFmtId="164">
+    <cacheField name="KL BG" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Đơn vị nhận" numFmtId="0">
@@ -1684,7 +1687,7 @@
     <n v="1"/>
     <n v="22755.43"/>
     <s v="PAC"/>
-    <s v="V314-5"/>
+    <s v="V314-005"/>
   </r>
   <r>
     <n v="4"/>
@@ -2179,7 +2182,7 @@
     <n v="1"/>
     <n v="23721.187999999995"/>
     <s v="PAC"/>
-    <s v="V314-4"/>
+    <s v="V314-004"/>
   </r>
   <r>
     <n v="13"/>
@@ -6583,27 +6586,27 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
@@ -6645,7 +6648,7 @@
   </colItems>
   <dataFields count="2">
     <dataField name="Sum of T.Weight" fld="15" baseField="1" baseItem="0"/>
-    <dataField name="Sum of KL Gá" fld="37" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Sum of KL Gá" fld="37" baseField="0" baseItem="0" numFmtId="43"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -6978,7 +6981,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:BH95"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -7028,7 +7031,7 @@
     <col min="60" max="60" width="14.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="25.5" customHeight="1" thickTop="1">
+    <row r="1" spans="1:60" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str">
         <f>"DỰ ÁN:"&amp;B4</f>
         <v>DỰ ÁN:V314</v>
@@ -7099,7 +7102,7 @@
       <c r="BC1" s="48"/>
       <c r="BD1" s="48"/>
     </row>
-    <row r="2" spans="1:60" ht="25.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:60" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
@@ -7124,7 +7127,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="51">
         <f ca="1">IF(WEEKDAY(TODAY()-1)=1,TODAY()-2,TODAY()-1)</f>
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="T2" s="13" t="s">
         <v>40</v>
@@ -7204,7 +7207,7 @@
       <c r="BC2" s="48"/>
       <c r="BD2" s="48"/>
     </row>
-    <row r="3" spans="1:60" ht="27" customHeight="1" thickTop="1">
+    <row r="3" spans="1:60" ht="27" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>7</v>
       </c>
@@ -7383,7 +7386,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:60">
+    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
         <f>IF(B4="","",SUBTOTAL(3,$B$4:B4))</f>
         <v>1</v>
@@ -7516,7 +7519,7 @@
         <v>189764.41100000002</v>
       </c>
     </row>
-    <row r="5" spans="1:60">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
         <f>IF(B5="","",SUBTOTAL(3,$B$4:B5))</f>
         <v>2</v>
@@ -7649,7 +7652,7 @@
         <v>189764.41100000002</v>
       </c>
     </row>
-    <row r="6" spans="1:60">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A6" s="24">
         <f>IF(B6="","",SUBTOTAL(3,$B$4:B6))</f>
         <v>3</v>
@@ -7794,7 +7797,7 @@
         <v>189764.41100000002</v>
       </c>
     </row>
-    <row r="7" spans="1:60">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A7" s="24">
         <f>IF(B7="","",SUBTOTAL(3,$B$4:B7))</f>
         <v>4</v>
@@ -7927,7 +7930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:60">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A8" s="24">
         <f>IF(B8="","",SUBTOTAL(3,$B$4:B8))</f>
         <v>5</v>
@@ -8060,7 +8063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:60">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A9" s="24">
         <f>IF(B9="","",SUBTOTAL(3,$B$4:B9))</f>
         <v>6</v>
@@ -8193,7 +8196,7 @@
         <v>189764.41100000002</v>
       </c>
     </row>
-    <row r="10" spans="1:60">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
         <f>IF(B10="","",SUBTOTAL(3,$B$4:B10))</f>
         <v>7</v>
@@ -8317,7 +8320,7 @@
       <c r="BC10" s="71"/>
       <c r="BD10" s="71"/>
     </row>
-    <row r="11" spans="1:60">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
         <f>IF(B11="","",SUBTOTAL(3,$B$4:B11))</f>
         <v>8</v>
@@ -8441,7 +8444,7 @@
       <c r="BC11" s="71"/>
       <c r="BD11" s="71"/>
     </row>
-    <row r="12" spans="1:60">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A12" s="24">
         <f>IF(B12="","",SUBTOTAL(3,$B$4:B12))</f>
         <v>9</v>
@@ -8565,7 +8568,7 @@
       <c r="BC12" s="71"/>
       <c r="BD12" s="71"/>
     </row>
-    <row r="13" spans="1:60">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A13" s="24">
         <f>IF(B13="","",SUBTOTAL(3,$B$4:B13))</f>
         <v>10</v>
@@ -8689,7 +8692,7 @@
       <c r="BC13" s="71"/>
       <c r="BD13" s="71"/>
     </row>
-    <row r="14" spans="1:60">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A14" s="24">
         <f>IF(B14="","",SUBTOTAL(3,$B$4:B14))</f>
         <v>11</v>
@@ -8813,7 +8816,7 @@
       <c r="BC14" s="71"/>
       <c r="BD14" s="71"/>
     </row>
-    <row r="15" spans="1:60">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A15" s="24">
         <f>IF(B15="","",SUBTOTAL(3,$B$4:B15))</f>
         <v>12</v>
@@ -8949,7 +8952,7 @@
       <c r="BC15" s="71"/>
       <c r="BD15" s="71"/>
     </row>
-    <row r="16" spans="1:60">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
         <f>IF(B16="","",SUBTOTAL(3,$B$4:B16))</f>
         <v>13</v>
@@ -9073,7 +9076,7 @@
       <c r="BC16" s="71"/>
       <c r="BD16" s="71"/>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A17" s="24">
         <f>IF(B17="","",SUBTOTAL(3,$B$4:B17))</f>
         <v>14</v>
@@ -9197,7 +9200,7 @@
       <c r="BC17" s="71"/>
       <c r="BD17" s="71"/>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
         <f>IF(B18="","",SUBTOTAL(3,$B$4:B18))</f>
         <v>15</v>
@@ -9321,7 +9324,7 @@
       <c r="BC18" s="71"/>
       <c r="BD18" s="71"/>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A19" s="24">
         <f>IF(B19="","",SUBTOTAL(3,$B$4:B19))</f>
         <v>16</v>
@@ -9445,7 +9448,7 @@
       <c r="BC19" s="71"/>
       <c r="BD19" s="71"/>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A20" s="24">
         <f>IF(B20="","",SUBTOTAL(3,$B$4:B20))</f>
         <v>17</v>
@@ -9581,7 +9584,7 @@
       <c r="BC20" s="71"/>
       <c r="BD20" s="71"/>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A21" s="24">
         <f>IF(B21="","",SUBTOTAL(3,$B$4:B21))</f>
         <v>18</v>
@@ -9717,7 +9720,7 @@
       <c r="BC21" s="71"/>
       <c r="BD21" s="71"/>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A22" s="24">
         <f>IF(B22="","",SUBTOTAL(3,$B$4:B22))</f>
         <v>19</v>
@@ -9853,7 +9856,7 @@
       <c r="BC22" s="71"/>
       <c r="BD22" s="71"/>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A23" s="24">
         <f>IF(B23="","",SUBTOTAL(3,$B$4:B23))</f>
         <v>20</v>
@@ -9989,7 +9992,7 @@
       <c r="BC23" s="71"/>
       <c r="BD23" s="71"/>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A24" s="24">
         <f>IF(B24="","",SUBTOTAL(3,$B$4:B24))</f>
         <v>21</v>
@@ -10125,7 +10128,7 @@
       <c r="BC24" s="71"/>
       <c r="BD24" s="71"/>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A25" s="24">
         <f>IF(B25="","",SUBTOTAL(3,$B$4:B25))</f>
         <v>22</v>
@@ -10261,7 +10264,7 @@
       <c r="BC25" s="71"/>
       <c r="BD25" s="71"/>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A26" s="24">
         <f>IF(B26="","",SUBTOTAL(3,$B$4:B26))</f>
         <v>23</v>
@@ -10375,7 +10378,7 @@
       <c r="BC26" s="71"/>
       <c r="BD26" s="71"/>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A27" s="24">
         <f>IF(B27="","",SUBTOTAL(3,$B$4:B27))</f>
         <v>24</v>
@@ -10402,7 +10405,7 @@
       </c>
       <c r="I27" s="25"/>
       <c r="J27" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K27" s="27" t="s">
         <v>115</v>
@@ -10491,7 +10494,7 @@
       <c r="BC27" s="71"/>
       <c r="BD27" s="71"/>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A28" s="24">
         <f>IF(B28="","",SUBTOTAL(3,$B$4:B28))</f>
         <v>25</v>
@@ -10518,7 +10521,7 @@
       </c>
       <c r="I28" s="25"/>
       <c r="J28" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K28" s="27" t="s">
         <v>117</v>
@@ -10607,7 +10610,7 @@
       <c r="BC28" s="71"/>
       <c r="BD28" s="71"/>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A29" s="24">
         <f>IF(B29="","",SUBTOTAL(3,$B$4:B29))</f>
         <v>26</v>
@@ -10634,7 +10637,7 @@
       </c>
       <c r="I29" s="25"/>
       <c r="J29" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K29" s="27" t="s">
         <v>119</v>
@@ -10723,7 +10726,7 @@
       <c r="BC29" s="71"/>
       <c r="BD29" s="71"/>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A30" s="24">
         <f>IF(B30="","",SUBTOTAL(3,$B$4:B30))</f>
         <v>27</v>
@@ -10750,7 +10753,7 @@
       </c>
       <c r="I30" s="25"/>
       <c r="J30" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K30" s="27" t="s">
         <v>121</v>
@@ -10839,7 +10842,7 @@
       <c r="BC30" s="71"/>
       <c r="BD30" s="71"/>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A31" s="24">
         <f>IF(B31="","",SUBTOTAL(3,$B$4:B31))</f>
         <v>28</v>
@@ -10866,7 +10869,7 @@
       </c>
       <c r="I31" s="25"/>
       <c r="J31" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K31" s="27" t="s">
         <v>123</v>
@@ -10955,7 +10958,7 @@
       <c r="BC31" s="71"/>
       <c r="BD31" s="71"/>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A32" s="24">
         <f>IF(B32="","",SUBTOTAL(3,$B$4:B32))</f>
         <v>29</v>
@@ -10982,7 +10985,7 @@
       </c>
       <c r="I32" s="25"/>
       <c r="J32" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K32" s="27" t="s">
         <v>125</v>
@@ -11071,7 +11074,7 @@
       <c r="BC32" s="71"/>
       <c r="BD32" s="71"/>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A33" s="24">
         <f>IF(B33="","",SUBTOTAL(3,$B$4:B33))</f>
         <v>30</v>
@@ -11098,7 +11101,7 @@
       </c>
       <c r="I33" s="25"/>
       <c r="J33" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K33" s="27" t="s">
         <v>127</v>
@@ -11187,7 +11190,7 @@
       <c r="BC33" s="71"/>
       <c r="BD33" s="71"/>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A34" s="24">
         <f>IF(B34="","",SUBTOTAL(3,$B$4:B34))</f>
         <v>31</v>
@@ -11214,7 +11217,7 @@
       </c>
       <c r="I34" s="25"/>
       <c r="J34" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K34" s="27" t="s">
         <v>129</v>
@@ -11303,7 +11306,7 @@
       <c r="BC34" s="71"/>
       <c r="BD34" s="71"/>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A35" s="24">
         <f>IF(B35="","",SUBTOTAL(3,$B$4:B35))</f>
         <v>32</v>
@@ -11330,7 +11333,7 @@
       </c>
       <c r="I35" s="25"/>
       <c r="J35" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K35" s="27" t="s">
         <v>131</v>
@@ -11419,7 +11422,7 @@
       <c r="BC35" s="71"/>
       <c r="BD35" s="71"/>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A36" s="24">
         <f>IF(B36="","",SUBTOTAL(3,$B$4:B36))</f>
         <v>33</v>
@@ -11446,7 +11449,7 @@
       </c>
       <c r="I36" s="25"/>
       <c r="J36" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K36" s="27" t="s">
         <v>133</v>
@@ -11535,7 +11538,7 @@
       <c r="BC36" s="71"/>
       <c r="BD36" s="71"/>
     </row>
-    <row r="37" spans="1:56">
+    <row r="37" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A37" s="24">
         <f>IF(B37="","",SUBTOTAL(3,$B$4:B37))</f>
         <v>34</v>
@@ -11562,7 +11565,7 @@
       </c>
       <c r="I37" s="25"/>
       <c r="J37" s="26" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K37" s="27" t="s">
         <v>135</v>
@@ -11651,7 +11654,7 @@
       <c r="BC37" s="71"/>
       <c r="BD37" s="71"/>
     </row>
-    <row r="38" spans="1:56">
+    <row r="38" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A38" s="24">
         <f>IF(B38="","",SUBTOTAL(3,$B$4:B38))</f>
         <v>35</v>
@@ -11767,7 +11770,7 @@
       <c r="BC38" s="71"/>
       <c r="BD38" s="71"/>
     </row>
-    <row r="39" spans="1:56">
+    <row r="39" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A39" s="24">
         <f>IF(B39="","",SUBTOTAL(3,$B$4:B39))</f>
         <v>36</v>
@@ -11883,7 +11886,7 @@
       <c r="BC39" s="71"/>
       <c r="BD39" s="71"/>
     </row>
-    <row r="40" spans="1:56">
+    <row r="40" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A40" s="24">
         <f>IF(B40="","",SUBTOTAL(3,$B$4:B40))</f>
         <v>37</v>
@@ -11999,7 +12002,7 @@
       <c r="BC40" s="71"/>
       <c r="BD40" s="71"/>
     </row>
-    <row r="41" spans="1:56">
+    <row r="41" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A41" s="24">
         <f>IF(B41="","",SUBTOTAL(3,$B$4:B41))</f>
         <v>38</v>
@@ -12115,7 +12118,7 @@
       <c r="BC41" s="71"/>
       <c r="BD41" s="71"/>
     </row>
-    <row r="42" spans="1:56">
+    <row r="42" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A42" s="24">
         <f>IF(B42="","",SUBTOTAL(3,$B$4:B42))</f>
         <v>39</v>
@@ -12231,7 +12234,7 @@
       <c r="BC42" s="71"/>
       <c r="BD42" s="71"/>
     </row>
-    <row r="43" spans="1:56">
+    <row r="43" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A43" s="24">
         <f>IF(B43="","",SUBTOTAL(3,$B$4:B43))</f>
         <v>40</v>
@@ -12347,7 +12350,7 @@
       <c r="BC43" s="71"/>
       <c r="BD43" s="71"/>
     </row>
-    <row r="44" spans="1:56">
+    <row r="44" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A44" s="24">
         <f>IF(B44="","",SUBTOTAL(3,$B$4:B44))</f>
         <v>41</v>
@@ -12463,7 +12466,7 @@
       <c r="BC44" s="71"/>
       <c r="BD44" s="71"/>
     </row>
-    <row r="45" spans="1:56">
+    <row r="45" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A45" s="24">
         <f>IF(B45="","",SUBTOTAL(3,$B$4:B45))</f>
         <v>42</v>
@@ -12579,7 +12582,7 @@
       <c r="BC45" s="71"/>
       <c r="BD45" s="71"/>
     </row>
-    <row r="46" spans="1:56">
+    <row r="46" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A46" s="24">
         <f>IF(B46="","",SUBTOTAL(3,$B$4:B46))</f>
         <v>43</v>
@@ -12695,7 +12698,7 @@
       <c r="BC46" s="71"/>
       <c r="BD46" s="71"/>
     </row>
-    <row r="47" spans="1:56">
+    <row r="47" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A47" s="24">
         <f>IF(B47="","",SUBTOTAL(3,$B$4:B47))</f>
         <v>44</v>
@@ -12811,7 +12814,7 @@
       <c r="BC47" s="71"/>
       <c r="BD47" s="71"/>
     </row>
-    <row r="48" spans="1:56">
+    <row r="48" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A48" s="24">
         <f>IF(B48="","",SUBTOTAL(3,$B$4:B48))</f>
         <v>45</v>
@@ -12927,7 +12930,7 @@
       <c r="BC48" s="71"/>
       <c r="BD48" s="71"/>
     </row>
-    <row r="49" spans="1:56">
+    <row r="49" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A49" s="24">
         <f>IF(B49="","",SUBTOTAL(3,$B$4:B49))</f>
         <v>46</v>
@@ -13043,7 +13046,7 @@
       <c r="BC49" s="71"/>
       <c r="BD49" s="71"/>
     </row>
-    <row r="50" spans="1:56">
+    <row r="50" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A50" s="24">
         <f>IF(B50="","",SUBTOTAL(3,$B$4:B50))</f>
         <v>47</v>
@@ -13159,7 +13162,7 @@
       <c r="BC50" s="71"/>
       <c r="BD50" s="71"/>
     </row>
-    <row r="51" spans="1:56">
+    <row r="51" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A51" s="24">
         <f>IF(B51="","",SUBTOTAL(3,$B$4:B51))</f>
         <v>48</v>
@@ -13275,7 +13278,7 @@
       <c r="BC51" s="71"/>
       <c r="BD51" s="71"/>
     </row>
-    <row r="52" spans="1:56">
+    <row r="52" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A52" s="24">
         <f>IF(B52="","",SUBTOTAL(3,$B$4:B52))</f>
         <v>49</v>
@@ -13391,7 +13394,7 @@
       <c r="BC52" s="71"/>
       <c r="BD52" s="71"/>
     </row>
-    <row r="53" spans="1:56">
+    <row r="53" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A53" s="24">
         <f>IF(B53="","",SUBTOTAL(3,$B$4:B53))</f>
         <v>50</v>
@@ -13507,7 +13510,7 @@
       <c r="BC53" s="71"/>
       <c r="BD53" s="71"/>
     </row>
-    <row r="54" spans="1:56">
+    <row r="54" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A54" s="24">
         <f>IF(B54="","",SUBTOTAL(3,$B$4:B54))</f>
         <v>51</v>
@@ -13623,7 +13626,7 @@
       <c r="BC54" s="71"/>
       <c r="BD54" s="71"/>
     </row>
-    <row r="55" spans="1:56">
+    <row r="55" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A55" s="24">
         <f>IF(B55="","",SUBTOTAL(3,$B$4:B55))</f>
         <v>52</v>
@@ -13739,7 +13742,7 @@
       <c r="BC55" s="71"/>
       <c r="BD55" s="71"/>
     </row>
-    <row r="56" spans="1:56">
+    <row r="56" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A56" s="24">
         <f>IF(B56="","",SUBTOTAL(3,$B$4:B56))</f>
         <v>53</v>
@@ -13855,7 +13858,7 @@
       <c r="BC56" s="71"/>
       <c r="BD56" s="71"/>
     </row>
-    <row r="57" spans="1:56">
+    <row r="57" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A57" s="24">
         <f>IF(B57="","",SUBTOTAL(3,$B$4:B57))</f>
         <v>54</v>
@@ -13971,7 +13974,7 @@
       <c r="BC57" s="71"/>
       <c r="BD57" s="71"/>
     </row>
-    <row r="58" spans="1:56">
+    <row r="58" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A58" s="24">
         <f>IF(B58="","",SUBTOTAL(3,$B$4:B58))</f>
         <v>55</v>
@@ -14087,7 +14090,7 @@
       <c r="BC58" s="71"/>
       <c r="BD58" s="71"/>
     </row>
-    <row r="59" spans="1:56">
+    <row r="59" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A59" s="24">
         <f>IF(B59="","",SUBTOTAL(3,$B$4:B59))</f>
         <v>56</v>
@@ -14203,7 +14206,7 @@
       <c r="BC59" s="71"/>
       <c r="BD59" s="71"/>
     </row>
-    <row r="60" spans="1:56">
+    <row r="60" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A60" s="24">
         <f>IF(B60="","",SUBTOTAL(3,$B$4:B60))</f>
         <v>57</v>
@@ -14319,7 +14322,7 @@
       <c r="BC60" s="71"/>
       <c r="BD60" s="71"/>
     </row>
-    <row r="61" spans="1:56">
+    <row r="61" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A61" s="24">
         <f>IF(B61="","",SUBTOTAL(3,$B$4:B61))</f>
         <v>58</v>
@@ -14435,7 +14438,7 @@
       <c r="BC61" s="71"/>
       <c r="BD61" s="71"/>
     </row>
-    <row r="62" spans="1:56">
+    <row r="62" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A62" s="24">
         <f>IF(B62="","",SUBTOTAL(3,$B$4:B62))</f>
         <v>59</v>
@@ -14551,7 +14554,7 @@
       <c r="BC62" s="71"/>
       <c r="BD62" s="71"/>
     </row>
-    <row r="63" spans="1:56">
+    <row r="63" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A63" s="24">
         <f>IF(B63="","",SUBTOTAL(3,$B$4:B63))</f>
         <v>60</v>
@@ -14667,7 +14670,7 @@
       <c r="BC63" s="71"/>
       <c r="BD63" s="71"/>
     </row>
-    <row r="64" spans="1:56">
+    <row r="64" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A64" s="24">
         <f>IF(B64="","",SUBTOTAL(3,$B$4:B64))</f>
         <v>61</v>
@@ -14783,7 +14786,7 @@
       <c r="BC64" s="71"/>
       <c r="BD64" s="71"/>
     </row>
-    <row r="65" spans="1:56">
+    <row r="65" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A65" s="24">
         <f>IF(B65="","",SUBTOTAL(3,$B$4:B65))</f>
         <v>62</v>
@@ -14899,7 +14902,7 @@
       <c r="BC65" s="71"/>
       <c r="BD65" s="71"/>
     </row>
-    <row r="66" spans="1:56">
+    <row r="66" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A66" s="24">
         <f>IF(B66="","",SUBTOTAL(3,$B$4:B66))</f>
         <v>63</v>
@@ -15013,7 +15016,7 @@
       <c r="BC66" s="71"/>
       <c r="BD66" s="71"/>
     </row>
-    <row r="67" spans="1:56">
+    <row r="67" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A67" s="24">
         <f>IF(B67="","",SUBTOTAL(3,$B$4:B67))</f>
         <v>64</v>
@@ -15129,7 +15132,7 @@
       <c r="BC67" s="71"/>
       <c r="BD67" s="71"/>
     </row>
-    <row r="68" spans="1:56">
+    <row r="68" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A68" s="24">
         <f>IF(B68="","",SUBTOTAL(3,$B$4:B68))</f>
         <v>65</v>
@@ -15245,7 +15248,7 @@
       <c r="BC68" s="71"/>
       <c r="BD68" s="71"/>
     </row>
-    <row r="69" spans="1:56">
+    <row r="69" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A69" s="24">
         <f>IF(B69="","",SUBTOTAL(3,$B$4:B69))</f>
         <v>66</v>
@@ -15361,7 +15364,7 @@
       <c r="BC69" s="71"/>
       <c r="BD69" s="71"/>
     </row>
-    <row r="70" spans="1:56">
+    <row r="70" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A70" s="24">
         <f>IF(B70="","",SUBTOTAL(3,$B$4:B70))</f>
         <v>67</v>
@@ -15477,7 +15480,7 @@
       <c r="BC70" s="71"/>
       <c r="BD70" s="71"/>
     </row>
-    <row r="71" spans="1:56">
+    <row r="71" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A71" s="24">
         <f>IF(B71="","",SUBTOTAL(3,$B$4:B71))</f>
         <v>68</v>
@@ -15593,7 +15596,7 @@
       <c r="BC71" s="71"/>
       <c r="BD71" s="71"/>
     </row>
-    <row r="72" spans="1:56">
+    <row r="72" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A72" s="24">
         <f>IF(B72="","",SUBTOTAL(3,$B$4:B72))</f>
         <v>69</v>
@@ -15709,7 +15712,7 @@
       <c r="BC72" s="71"/>
       <c r="BD72" s="71"/>
     </row>
-    <row r="73" spans="1:56">
+    <row r="73" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A73" s="24" t="str">
         <f>IF(B73="","",SUBTOTAL(3,$B$4:B73))</f>
         <v/>
@@ -15797,7 +15800,7 @@
       <c r="BC73" s="71"/>
       <c r="BD73" s="71"/>
     </row>
-    <row r="74" spans="1:56">
+    <row r="74" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A74" s="24" t="str">
         <f>IF(B74="","",SUBTOTAL(3,$B$4:B74))</f>
         <v/>
@@ -15885,7 +15888,7 @@
       <c r="BC74" s="71"/>
       <c r="BD74" s="71"/>
     </row>
-    <row r="75" spans="1:56">
+    <row r="75" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A75" s="24" t="str">
         <f>IF(B75="","",SUBTOTAL(3,$B$4:B75))</f>
         <v/>
@@ -15973,7 +15976,7 @@
       <c r="BC75" s="71"/>
       <c r="BD75" s="71"/>
     </row>
-    <row r="76" spans="1:56">
+    <row r="76" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A76" s="24" t="str">
         <f>IF(B76="","",SUBTOTAL(3,$B$4:B76))</f>
         <v/>
@@ -16061,7 +16064,7 @@
       <c r="BC76" s="71"/>
       <c r="BD76" s="71"/>
     </row>
-    <row r="77" spans="1:56">
+    <row r="77" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A77" s="24" t="str">
         <f>IF(B77="","",SUBTOTAL(3,$B$4:B77))</f>
         <v/>
@@ -16149,7 +16152,7 @@
       <c r="BC77" s="71"/>
       <c r="BD77" s="71"/>
     </row>
-    <row r="78" spans="1:56">
+    <row r="78" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A78" s="24" t="str">
         <f>IF(B78="","",SUBTOTAL(3,$B$4:B78))</f>
         <v/>
@@ -16237,7 +16240,7 @@
       <c r="BC78" s="71"/>
       <c r="BD78" s="71"/>
     </row>
-    <row r="79" spans="1:56">
+    <row r="79" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A79" s="24" t="str">
         <f>IF(B79="","",SUBTOTAL(3,$B$4:B79))</f>
         <v/>
@@ -16325,7 +16328,7 @@
       <c r="BC79" s="71"/>
       <c r="BD79" s="71"/>
     </row>
-    <row r="80" spans="1:56">
+    <row r="80" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A80" s="24" t="str">
         <f>IF(B80="","",SUBTOTAL(3,$B$4:B80))</f>
         <v/>
@@ -16413,7 +16416,7 @@
       <c r="BC80" s="71"/>
       <c r="BD80" s="71"/>
     </row>
-    <row r="81" spans="1:56">
+    <row r="81" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A81" s="24" t="str">
         <f>IF(B81="","",SUBTOTAL(3,$B$4:B81))</f>
         <v/>
@@ -16501,7 +16504,7 @@
       <c r="BC81" s="71"/>
       <c r="BD81" s="71"/>
     </row>
-    <row r="82" spans="1:56">
+    <row r="82" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A82" s="24" t="str">
         <f>IF(B82="","",SUBTOTAL(3,$B$4:B82))</f>
         <v/>
@@ -16589,7 +16592,7 @@
       <c r="BC82" s="71"/>
       <c r="BD82" s="71"/>
     </row>
-    <row r="83" spans="1:56">
+    <row r="83" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A83" s="24" t="str">
         <f>IF(B83="","",SUBTOTAL(3,$B$4:B83))</f>
         <v/>
@@ -16677,7 +16680,7 @@
       <c r="BC83" s="71"/>
       <c r="BD83" s="71"/>
     </row>
-    <row r="84" spans="1:56">
+    <row r="84" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A84" s="24" t="str">
         <f>IF(B84="","",SUBTOTAL(3,$B$4:B84))</f>
         <v/>
@@ -16765,7 +16768,7 @@
       <c r="BC84" s="71"/>
       <c r="BD84" s="71"/>
     </row>
-    <row r="85" spans="1:56">
+    <row r="85" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A85" s="24" t="str">
         <f>IF(B85="","",SUBTOTAL(3,$B$4:B85))</f>
         <v/>
@@ -16853,7 +16856,7 @@
       <c r="BC85" s="71"/>
       <c r="BD85" s="71"/>
     </row>
-    <row r="86" spans="1:56">
+    <row r="86" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A86" s="24" t="str">
         <f>IF(B86="","",SUBTOTAL(3,$B$4:B86))</f>
         <v/>
@@ -16941,7 +16944,7 @@
       <c r="BC86" s="71"/>
       <c r="BD86" s="71"/>
     </row>
-    <row r="87" spans="1:56">
+    <row r="87" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A87" s="24" t="str">
         <f>IF(B87="","",SUBTOTAL(3,$B$4:B87))</f>
         <v/>
@@ -17029,7 +17032,7 @@
       <c r="BC87" s="71"/>
       <c r="BD87" s="71"/>
     </row>
-    <row r="88" spans="1:56">
+    <row r="88" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A88" s="24" t="str">
         <f>IF(B88="","",SUBTOTAL(3,$B$4:B88))</f>
         <v/>
@@ -17117,7 +17120,7 @@
       <c r="BC88" s="71"/>
       <c r="BD88" s="71"/>
     </row>
-    <row r="89" spans="1:56">
+    <row r="89" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A89" s="24" t="str">
         <f>IF(B89="","",SUBTOTAL(3,$B$4:B89))</f>
         <v/>
@@ -17205,7 +17208,7 @@
       <c r="BC89" s="71"/>
       <c r="BD89" s="71"/>
     </row>
-    <row r="90" spans="1:56">
+    <row r="90" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A90" s="24" t="str">
         <f>IF(B90="","",SUBTOTAL(3,$B$4:B90))</f>
         <v/>
@@ -17293,7 +17296,7 @@
       <c r="BC90" s="71"/>
       <c r="BD90" s="71"/>
     </row>
-    <row r="91" spans="1:56">
+    <row r="91" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A91" s="24" t="str">
         <f>IF(B91="","",SUBTOTAL(3,$B$4:B91))</f>
         <v/>
@@ -17381,7 +17384,7 @@
       <c r="BC91" s="71"/>
       <c r="BD91" s="71"/>
     </row>
-    <row r="92" spans="1:56">
+    <row r="92" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A92" s="24" t="str">
         <f>IF(B92="","",SUBTOTAL(3,$B$4:B92))</f>
         <v/>
@@ -17469,7 +17472,7 @@
       <c r="BC92" s="71"/>
       <c r="BD92" s="71"/>
     </row>
-    <row r="93" spans="1:56">
+    <row r="93" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A93" s="24" t="str">
         <f>IF(B93="","",SUBTOTAL(3,$B$4:B93))</f>
         <v/>
@@ -17557,7 +17560,7 @@
       <c r="BC93" s="71"/>
       <c r="BD93" s="71"/>
     </row>
-    <row r="94" spans="1:56" ht="16.5" thickBot="1">
+    <row r="94" spans="1:56" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="38" t="str">
         <f>IF(B94="","",SUBTOTAL(3,$B$4:B94))</f>
         <v/>
@@ -17645,10 +17648,10 @@
       <c r="BC94" s="71"/>
       <c r="BD94" s="71"/>
     </row>
-    <row r="95" spans="1:56" ht="16.5" thickTop="1"/>
+    <row r="95" spans="1:56" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A3:BD94" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}"/>
-  <conditionalFormatting sqref="A4:AG94 AJ4:AL94">
+  <conditionalFormatting sqref="AJ4:AL94 A4:AG94">
     <cfRule type="expression" dxfId="5" priority="2">
       <formula>$AK4=$N4</formula>
     </cfRule>

--- a/03.QLDA/V314.xlsx
+++ b/03.QLDA/V314.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMECC JSC\Amecc 2\00. Overall Report\03.QLDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7065DA-D6D0-450C-AFD0-3B5C4B67F9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7807F674-6530-48C0-A416-E1824FD6C38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
   </bookViews>
@@ -55,9 +55,9 @@
     <definedName name="ㅋㅋㅋㅋㅋㅋㅋㅋㅋ" hidden="1">#REF!</definedName>
     <definedName name="ㅌㅊㅍㅌㅊㅍㅌㅋㅊㅍㅌ" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId2"/>
+    <pivotCache cacheId="128" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46295.790670949071" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="91" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46314.366415625002" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="91" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A3:BA94" sheet="Progress"/>
   </cacheSource>
@@ -1460,7 +1460,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="7116.3563999999978"/>
     </cacheField>
     <cacheField name="Ngày Gá" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-06-03T00:00:00" maxDate="2026-08-06T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-06-03T00:00:00" maxDate="2026-10-17T00:00:00"/>
     </cacheField>
     <cacheField name="SL Gá" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
@@ -1469,7 +1469,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="23721.187999999995"/>
     </cacheField>
     <cacheField name="Ngày Hàn" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-06-14T00:00:00" maxDate="2026-08-09T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-06-14T00:00:00" maxDate="2026-10-17T00:00:00"/>
     </cacheField>
     <cacheField name="SL Hàn" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
@@ -2765,14 +2765,14 @@
     <m/>
     <m/>
     <m/>
-    <n v="0"/>
-    <n v="5316.6400000000012"/>
+    <n v="2658.3200000000006"/>
+    <n v="2658.3200000000006"/>
     <m/>
     <n v="0.3"/>
     <n v="1594.9920000000004"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-10-16T00:00:00"/>
+    <n v="1"/>
+    <n v="5316.6400000000012"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -2799,7 +2799,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DDO-OC270"/>
     <s v="CS31B"/>
     <s v="(1491 x 4691 x 12191)"/>
@@ -2854,7 +2854,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DDO-OC279"/>
     <s v="CS32B"/>
     <s v="(382 x 1595 x 11829)"/>
@@ -2909,7 +2909,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DDO-OC283"/>
     <s v="CS33B"/>
     <s v="(767 x 1157 x 11841)"/>
@@ -2964,7 +2964,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DDO-OC286"/>
     <s v="CS34B"/>
     <s v="(779 x 2795 x 11841)"/>
@@ -3019,7 +3019,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DD0-0C289"/>
     <s v="CS35B"/>
     <s v="(1345 x 3468.5 x 11691)"/>
@@ -3074,7 +3074,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DD0-0C294"/>
     <s v="CS36B"/>
     <s v="(541 x 2095 x 11691)"/>
@@ -3129,7 +3129,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DD0-0C298"/>
     <s v="CS37B"/>
     <s v="(1345 x 3367 x 11641)"/>
@@ -3184,7 +3184,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DDO-OC303"/>
     <s v="CS38B"/>
     <s v="(366 x 1645 x 11579)"/>
@@ -3239,7 +3239,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DD0-0C307"/>
     <s v="CS39B"/>
     <s v="(1295 x 3267 x 11591)"/>
@@ -3294,7 +3294,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DD0-0C312"/>
     <s v="CS40B"/>
     <s v="(491 x 2061 x 11579)"/>
@@ -3349,7 +3349,7 @@
     <d v="2026-06-30T00:00:00"/>
     <s v="HRSG"/>
     <m/>
-    <s v="S1"/>
+    <s v="S4"/>
     <s v="25HG015-DDO-OC315"/>
     <s v="CS41B"/>
     <s v="(525 x 1141 x 11591)"/>
@@ -3480,14 +3480,14 @@
     <m/>
     <m/>
     <m/>
-    <n v="0"/>
-    <n v="3892.7239999999997"/>
+    <n v="1946.3619999999999"/>
+    <n v="1946.3619999999999"/>
     <m/>
     <n v="0.3"/>
     <n v="1167.8172"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-10-16T00:00:00"/>
+    <n v="1"/>
+    <n v="3892.7239999999997"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -3535,14 +3535,14 @@
     <m/>
     <m/>
     <m/>
-    <n v="0"/>
-    <n v="3309.712"/>
+    <n v="1654.856"/>
+    <n v="1654.856"/>
     <m/>
     <n v="0.3"/>
     <n v="992.91359999999997"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-10-16T00:00:00"/>
+    <n v="1"/>
+    <n v="3309.712"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -3590,17 +3590,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="0"/>
-    <n v="3280.2600000000007"/>
+    <n v="2952.2340000000004"/>
+    <n v="328.02600000000029"/>
     <m/>
     <n v="0.3"/>
     <n v="984.0780000000002"/>
-    <m/>
-    <m/>
-    <n v="0"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-10-12T00:00:00"/>
+    <n v="1"/>
+    <n v="3280.2600000000007"/>
+    <d v="2026-10-15T00:00:00"/>
+    <n v="1"/>
+    <n v="3280.2600000000007"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -3645,14 +3645,14 @@
     <m/>
     <m/>
     <m/>
-    <n v="0"/>
-    <n v="3970.6840000000002"/>
+    <n v="1985.3420000000001"/>
+    <n v="1985.3420000000001"/>
     <m/>
     <n v="0.3"/>
     <n v="1191.2052000000001"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-10-13T00:00:00"/>
+    <n v="1"/>
+    <n v="3970.6840000000002"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -3700,17 +3700,17 @@
     <m/>
     <m/>
     <m/>
-    <n v="0"/>
-    <n v="4347.7700000000004"/>
+    <n v="3912.9930000000004"/>
+    <n v="434.77700000000004"/>
     <m/>
     <n v="0.3"/>
     <n v="1304.3310000000001"/>
-    <m/>
-    <m/>
-    <n v="0"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-10-12T00:00:00"/>
+    <n v="1"/>
+    <n v="4347.7700000000004"/>
+    <d v="2026-10-16T00:00:00"/>
+    <n v="1"/>
+    <n v="4347.7700000000004"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -6533,7 +6533,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="128" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BF3:BH9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="53">
     <pivotField showAll="0"/>
@@ -7127,7 +7127,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="51">
         <f ca="1">IF(WEEKDAY(TODAY()-1)=1,TODAY()-2,TODAY()-1)</f>
-        <v>46294</v>
+        <v>46312</v>
       </c>
       <c r="T2" s="13" t="s">
         <v>40</v>
@@ -7152,20 +7152,20 @@
       <c r="AJ2" s="15"/>
       <c r="AK2" s="67">
         <f>SUBTOTAL(9,AK4:AK94)</f>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AL2" s="68">
         <f>SUBTOTAL(9,AL4:AL94)</f>
-        <v>189764.41100000002</v>
+        <v>217209.09500000003</v>
       </c>
       <c r="AM2" s="15"/>
       <c r="AN2" s="67">
         <f>SUBTOTAL(9,AN4:AN94)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO2" s="68">
         <f>SUBTOTAL(9,AO4:AO94)</f>
-        <v>189764.41100000002</v>
+        <v>197392.44100000002</v>
       </c>
       <c r="AP2" s="15"/>
       <c r="AQ2" s="67">
@@ -7516,7 +7516,7 @@
         <v>489671.35100000008</v>
       </c>
       <c r="BH4" s="70">
-        <v>189764.41100000002</v>
+        <v>213882.20100000003</v>
       </c>
     </row>
     <row r="5" spans="1:60" x14ac:dyDescent="0.25">
@@ -7649,7 +7649,7 @@
         <v>272462.25600000005</v>
       </c>
       <c r="BH5" s="70">
-        <v>189764.41100000002</v>
+        <v>213882.20100000003</v>
       </c>
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.25">
@@ -7794,7 +7794,7 @@
         <v>272462.25600000005</v>
       </c>
       <c r="BH6" s="70">
-        <v>189764.41100000002</v>
+        <v>213882.20100000003</v>
       </c>
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.25">
@@ -8193,7 +8193,7 @@
         <v>489671.35100000008</v>
       </c>
       <c r="BH9" s="70">
-        <v>189764.41100000002</v>
+        <v>213882.20100000003</v>
       </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.25">
@@ -10325,11 +10325,11 @@
       <c r="AD26" s="54"/>
       <c r="AE26" s="31">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2658.3200000000006</v>
       </c>
       <c r="AF26" s="32">
         <f t="shared" si="11"/>
-        <v>5316.6400000000012</v>
+        <v>2658.3200000000006</v>
       </c>
       <c r="AG26" s="30"/>
       <c r="AH26" s="33">
@@ -10339,11 +10339,15 @@
         <f t="shared" si="12"/>
         <v>1594.9920000000004</v>
       </c>
-      <c r="AJ26" s="35"/>
-      <c r="AK26" s="30"/>
+      <c r="AJ26" s="35">
+        <v>46311</v>
+      </c>
+      <c r="AK26" s="30">
+        <v>1</v>
+      </c>
       <c r="AL26" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>5316.6400000000012</v>
       </c>
       <c r="AM26" s="35"/>
       <c r="AN26" s="30"/>
@@ -11717,11 +11721,11 @@
       <c r="AD38" s="54"/>
       <c r="AE38" s="31">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1663.4470000000001</v>
       </c>
       <c r="AF38" s="32">
         <f t="shared" si="11"/>
-        <v>3326.8940000000002</v>
+        <v>1663.4470000000001</v>
       </c>
       <c r="AG38" s="30"/>
       <c r="AH38" s="33">
@@ -11731,11 +11735,15 @@
         <f t="shared" si="12"/>
         <v>998.06820000000005</v>
       </c>
-      <c r="AJ38" s="35"/>
-      <c r="AK38" s="30"/>
+      <c r="AJ38" s="35">
+        <v>46313</v>
+      </c>
+      <c r="AK38" s="30">
+        <v>1</v>
+      </c>
       <c r="AL38" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3326.8940000000002</v>
       </c>
       <c r="AM38" s="35"/>
       <c r="AN38" s="30"/>
@@ -11833,11 +11841,11 @@
       <c r="AD39" s="54"/>
       <c r="AE39" s="31">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1946.3619999999999</v>
       </c>
       <c r="AF39" s="32">
         <f t="shared" si="11"/>
-        <v>3892.7239999999997</v>
+        <v>1946.3619999999999</v>
       </c>
       <c r="AG39" s="30"/>
       <c r="AH39" s="33">
@@ -11847,11 +11855,15 @@
         <f t="shared" si="12"/>
         <v>1167.8172</v>
       </c>
-      <c r="AJ39" s="35"/>
-      <c r="AK39" s="30"/>
+      <c r="AJ39" s="35">
+        <v>46311</v>
+      </c>
+      <c r="AK39" s="30">
+        <v>1</v>
+      </c>
       <c r="AL39" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3892.7239999999997</v>
       </c>
       <c r="AM39" s="35"/>
       <c r="AN39" s="30"/>
@@ -11949,11 +11961,11 @@
       <c r="AD40" s="54"/>
       <c r="AE40" s="31">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1654.856</v>
       </c>
       <c r="AF40" s="32">
         <f t="shared" si="11"/>
-        <v>3309.712</v>
+        <v>1654.856</v>
       </c>
       <c r="AG40" s="30"/>
       <c r="AH40" s="33">
@@ -11963,11 +11975,15 @@
         <f t="shared" si="12"/>
         <v>992.91359999999997</v>
       </c>
-      <c r="AJ40" s="35"/>
-      <c r="AK40" s="30"/>
+      <c r="AJ40" s="35">
+        <v>46311</v>
+      </c>
+      <c r="AK40" s="30">
+        <v>1</v>
+      </c>
       <c r="AL40" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3309.712</v>
       </c>
       <c r="AM40" s="35"/>
       <c r="AN40" s="30"/>
@@ -12065,11 +12081,11 @@
       <c r="AD41" s="54"/>
       <c r="AE41" s="31">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2952.2340000000004</v>
       </c>
       <c r="AF41" s="32">
         <f t="shared" si="11"/>
-        <v>3280.2600000000007</v>
+        <v>328.02600000000029</v>
       </c>
       <c r="AG41" s="30"/>
       <c r="AH41" s="33">
@@ -12079,17 +12095,25 @@
         <f t="shared" si="12"/>
         <v>984.0780000000002</v>
       </c>
-      <c r="AJ41" s="35"/>
-      <c r="AK41" s="30"/>
+      <c r="AJ41" s="35">
+        <v>46307</v>
+      </c>
+      <c r="AK41" s="30">
+        <v>1</v>
+      </c>
       <c r="AL41" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AM41" s="35"/>
-      <c r="AN41" s="30"/>
+        <v>3280.2600000000007</v>
+      </c>
+      <c r="AM41" s="35">
+        <v>46310</v>
+      </c>
+      <c r="AN41" s="30">
+        <v>1</v>
+      </c>
       <c r="AO41" s="36">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3280.2600000000007</v>
       </c>
       <c r="AP41" s="35"/>
       <c r="AQ41" s="30"/>
@@ -12181,11 +12205,11 @@
       <c r="AD42" s="54"/>
       <c r="AE42" s="31">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1985.3420000000001</v>
       </c>
       <c r="AF42" s="32">
         <f t="shared" si="11"/>
-        <v>3970.6840000000002</v>
+        <v>1985.3420000000001</v>
       </c>
       <c r="AG42" s="30"/>
       <c r="AH42" s="33">
@@ -12195,11 +12219,15 @@
         <f t="shared" si="12"/>
         <v>1191.2052000000001</v>
       </c>
-      <c r="AJ42" s="35"/>
-      <c r="AK42" s="30"/>
+      <c r="AJ42" s="35">
+        <v>46308</v>
+      </c>
+      <c r="AK42" s="30">
+        <v>1</v>
+      </c>
       <c r="AL42" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3970.6840000000002</v>
       </c>
       <c r="AM42" s="35"/>
       <c r="AN42" s="30"/>
@@ -12297,11 +12325,11 @@
       <c r="AD43" s="54"/>
       <c r="AE43" s="31">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3912.9930000000004</v>
       </c>
       <c r="AF43" s="32">
         <f t="shared" si="11"/>
-        <v>4347.7700000000004</v>
+        <v>434.77700000000004</v>
       </c>
       <c r="AG43" s="30"/>
       <c r="AH43" s="33">
@@ -12311,17 +12339,25 @@
         <f t="shared" si="12"/>
         <v>1304.3310000000001</v>
       </c>
-      <c r="AJ43" s="35"/>
-      <c r="AK43" s="30"/>
+      <c r="AJ43" s="35">
+        <v>46307</v>
+      </c>
+      <c r="AK43" s="30">
+        <v>1</v>
+      </c>
       <c r="AL43" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AM43" s="35"/>
-      <c r="AN43" s="30"/>
+        <v>4347.7700000000004</v>
+      </c>
+      <c r="AM43" s="35">
+        <v>46311</v>
+      </c>
+      <c r="AN43" s="30">
+        <v>1</v>
+      </c>
       <c r="AO43" s="36">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>4347.7700000000004</v>
       </c>
       <c r="AP43" s="35"/>
       <c r="AQ43" s="30"/>
@@ -17651,7 +17687,7 @@
     <row r="95" spans="1:56" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A3:BD94" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}"/>
-  <conditionalFormatting sqref="AJ4:AL94 A4:AG94">
+  <conditionalFormatting sqref="A4:AG94 AJ4:AL94">
     <cfRule type="expression" dxfId="5" priority="2">
       <formula>$AK4=$N4</formula>
     </cfRule>
